--- a/CombinedBOM.xlsx
+++ b/CombinedBOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aweso\Documents\GitHub\Battery-Display\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F533EEA0-4B7E-49DE-9F06-7A71F814DE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A3D783-2F45-4AC2-A3E5-B215A8756FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EDE1EDCE-E545-4357-8981-634BEC06AA63}"/>
   </bookViews>
